--- a/data/50001485 - CALABRESSE METRO STO DOMINGO.xlsx
+++ b/data/50001485 - CALABRESSE METRO STO DOMINGO.xlsx
@@ -2758,7 +2758,7 @@
         <v>46106.60915392361</v>
       </c>
       <c r="D24" s="5">
-        <v>46223.60967895833</v>
+        <v>46279.42237763889</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
